--- a/simulations/correction_peat_market/AS_marché/AS_marché_hobby/inv/ARC_mark_pos.xlsx
+++ b/simulations/correction_peat_market/AS_marché/AS_marché_hobby/inv/ARC_mark_pos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\correction_peat_market\AS_marché\AS_marché_hobby\inv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210B47F2-9333-4090-A60B-081767C54C15}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6603076F-313C-4706-831A-4A16E4B5E33F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15200" windowHeight="6930" firstSheet="3" activeTab="5" xr2:uid="{B141029A-C238-484B-8693-F95FDEE8D83E}"/>
   </bookViews>
@@ -3030,8 +3030,8 @@
         <v>60</v>
       </c>
       <c r="B5">
-        <f>186611.81*(1+0.1)</f>
-        <v>205272.99100000001</v>
+        <f>186611.81*(1+0.8)</f>
+        <v>335901.25800000003</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -3044,8 +3044,8 @@
         <v>61</v>
       </c>
       <c r="B7">
-        <f>185060.41*(1+0.1)</f>
-        <v>203566.45100000003</v>
+        <f>185060.41*(1+0.8)</f>
+        <v>333108.73800000001</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
